--- a/logs/all_features_head_number/2_head_model_systematic_experiments/2_head_model_systematic_experiments.xlsx
+++ b/logs/all_features_head_number/2_head_model_systematic_experiments/2_head_model_systematic_experiments.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/2_head_model_systematic_experiments/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/all_features_head_number/2_head_model_systematic_experiments/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="179" documentId="11_3D6933BCD3C0D591904B0ED04B5ED87656CF7F9F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FFC9132-F722-4778-A18A-911277A2AE19}"/>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="8" r:id="rId5"/>
+    <pivotCache cacheId="10" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -690,7 +690,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -700,7 +700,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6653,7 +6652,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F6BFF658-778F-488E-A79F-972E77E6F35D}" name="TablaDinámica1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F6BFF658-778F-488E-A79F-972E77E6F35D}" name="TablaDinámica1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:N11" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="78">
     <pivotField numFmtId="164" showAll="0"/>
@@ -6871,7 +6870,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{55C44130-9661-4AFB-BB34-FB377E09B496}" name="TablaDinámica1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{55C44130-9661-4AFB-BB34-FB377E09B496}" name="TablaDinámica1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A1:G5" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="78">
     <pivotField numFmtId="164" showAll="0"/>
@@ -7048,7 +7047,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47942ECB-1301-4A6C-A9E6-877741A66FBD}" name="TablaDinámica2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47942ECB-1301-4A6C-A9E6-877741A66FBD}" name="TablaDinámica2" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A1:G5" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="78">
     <pivotField numFmtId="164" showAll="0"/>
@@ -24431,43 +24430,43 @@
       <c r="A4" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4">
         <v>0.79837269126723109</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4">
         <v>4.6446011319165557E-2</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4">
         <v>0.74268367978391958</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4">
         <v>4.1188565334818487E-3</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4">
         <v>0.51768219140644511</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4">
         <v>0.78349244936806539</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4">
         <v>0.8486063469408418</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4">
         <v>0.8209537314203269</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4">
         <v>-0.14348846168219995</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4">
         <v>0.14825071540850893</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4">
         <v>0.18220800403544474</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4">
         <v>-0.17049483162782558</v>
       </c>
-      <c r="N4" s="5">
+      <c r="N4">
         <v>10</v>
       </c>
     </row>
@@ -24475,43 +24474,43 @@
       <c r="A5" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5">
         <v>0.72318304464432115</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5">
         <v>-0.10407117936523416</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5">
         <v>0.6825815648175021</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5">
         <v>-0.12866168371564252</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5">
         <v>0.34624863362482539</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5">
         <v>0.74056275684539075</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5">
         <v>0.83658886815315425</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5">
         <v>0.80692600064663866</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5">
         <v>2.9307194582333745E-3</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5">
         <v>-0.10860595004750302</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5">
         <v>-0.14377723532911596</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M5">
         <v>-0.26519426894418691</v>
       </c>
-      <c r="N5" s="5">
+      <c r="N5">
         <v>10</v>
       </c>
     </row>
@@ -24519,43 +24518,43 @@
       <c r="A6" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>0.73787552569813697</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6">
         <v>-3.0734759923785392E-2</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6">
         <v>0.67146243664050664</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6">
         <v>-2.7176643183306065E-2</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6">
         <v>0.51710631003513474</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6">
         <v>0.78806970518430164</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6">
         <v>0.7958634128931823</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6">
         <v>0.58481031844940889</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6">
         <v>-0.11983411136176651</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6">
         <v>7.2182876151142744E-2</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6">
         <v>0.2672024144624493</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6">
         <v>-0.3282577519850518</v>
       </c>
-      <c r="N6" s="5">
+      <c r="N6">
         <v>10</v>
       </c>
     </row>
@@ -24563,43 +24562,43 @@
       <c r="A7" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7">
         <v>0.67156953460779056</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7">
         <v>0.14005292615305737</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7">
         <v>0.61653981776136002</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7">
         <v>0.14730460278992968</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7">
         <v>0.38201061472578379</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7">
         <v>0.66460521509168635</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7">
         <v>0.79240641063007855</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7">
         <v>0.62713703059789239</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7">
         <v>0.11419276824791177</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7">
         <v>0.55925132569425184</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7">
         <v>0.23291184896767758</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7">
         <v>-0.31713753175012294</v>
       </c>
-      <c r="N7" s="5">
+      <c r="N7">
         <v>10</v>
       </c>
     </row>
@@ -24607,43 +24606,43 @@
       <c r="A8" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8">
         <v>0.68768227034269214</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8">
         <v>-0.48541329254510152</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8">
         <v>0.60388019179225583</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8">
         <v>-0.43923592607775375</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8">
         <v>0.5270761317649747</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8">
         <v>0.7894720126576712</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8">
         <v>0.55655159038390767</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8">
         <v>0.5424210323624703</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8">
         <v>-0.2548541394764291</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K8">
         <v>-0.59048348606078371</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8">
         <v>-0.49969157038701056</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M8">
         <v>-0.41191450838679938</v>
       </c>
-      <c r="N8" s="5">
+      <c r="N8">
         <v>10</v>
       </c>
     </row>
@@ -24651,43 +24650,43 @@
       <c r="A9" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9">
         <v>0.63390336634964972</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9">
         <v>-0.18947755334049315</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9">
         <v>0.5601198844419264</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9">
         <v>-0.17298056794550734</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9">
         <v>0.4233572663255461</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9">
         <v>0.72039219763582474</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9">
         <v>0.53460462401043463</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9">
         <v>0.56212544979589985</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9">
         <v>-8.4323548288860239E-2</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9">
         <v>-3.6439240103808127E-2</v>
       </c>
-      <c r="L9" s="5">
+      <c r="L9">
         <v>-0.24703961117863327</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M9">
         <v>-0.32411987221072847</v>
       </c>
-      <c r="N9" s="5">
+      <c r="N9">
         <v>10</v>
       </c>
     </row>
@@ -24695,43 +24694,43 @@
       <c r="A10" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10">
         <v>0.62465319626362792</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10">
         <v>8.010325935082184E-2</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10">
         <v>0.54917314998860456</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10">
         <v>6.9831444130752665E-2</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10">
         <v>0.41979177808279555</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10">
         <v>0.67419516843582861</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10">
         <v>0.56208876154253973</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10">
         <v>0.54061689189325546</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10">
         <v>0.12588152921402246</v>
       </c>
-      <c r="K10" s="5">
+      <c r="K10">
         <v>0.35043541164812186</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L10">
         <v>8.5183976921129646E-3</v>
       </c>
-      <c r="M10" s="5">
+      <c r="M10">
         <v>-0.20550956203124321</v>
       </c>
-      <c r="N10" s="5">
+      <c r="N10">
         <v>10</v>
       </c>
     </row>
@@ -24739,43 +24738,43 @@
       <c r="A11" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11">
         <v>0.69674851845334951</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11">
         <v>-7.7584941193081375E-2</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11">
         <v>0.63234867503229641</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11">
         <v>-7.8114273924006467E-2</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11">
         <v>0.44761041799507223</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11">
         <v>0.73725564360268159</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11">
         <v>0.70381571636487728</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11">
         <v>0.64071292216655606</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11">
         <v>-5.1356463412726878E-2</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K11">
         <v>5.6370236098561517E-2</v>
       </c>
-      <c r="L11" s="5">
+      <c r="L11">
         <v>-2.8523964533867904E-2</v>
       </c>
-      <c r="M11" s="5">
+      <c r="M11">
         <v>-0.28894690384799393</v>
       </c>
-      <c r="N11" s="5">
+      <c r="N11">
         <v>70</v>
       </c>
     </row>
